--- a/Project_ETF/ETF_Investment_Portfolio/00981A/ETF_Investment_Portfolio_20260901.xlsx
+++ b/Project_ETF/ETF_Investment_Portfolio/00981A/ETF_Investment_Portfolio_20260901.xlsx
@@ -616,7 +616,7 @@
       </c>
       <c r="D21" s="4" t="inlineStr">
         <is>
-          <t>9.38%</t>
+          <t>9.23%</t>
         </is>
       </c>
     </row>
@@ -638,73 +638,73 @@
       </c>
       <c r="D22" s="4" t="inlineStr">
         <is>
-          <t>9.24%</t>
+          <t>9.21%</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="3" t="inlineStr">
         <is>
-          <t>3017</t>
+          <t>2454</t>
         </is>
       </c>
       <c r="B23" s="3" t="inlineStr">
         <is>
-          <t>奇鋐</t>
+          <t>聯發科</t>
         </is>
       </c>
       <c r="C23" s="4" t="inlineStr">
         <is>
-          <t>5,949,000</t>
+          <t>5,088,000</t>
         </is>
       </c>
       <c r="D23" s="4" t="inlineStr">
         <is>
-          <t>7.21%</t>
+          <t>7.54%</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="3" t="inlineStr">
         <is>
-          <t>3037</t>
+          <t>3017</t>
         </is>
       </c>
       <c r="B24" s="3" t="inlineStr">
         <is>
-          <t>欣興</t>
+          <t>奇鋐</t>
         </is>
       </c>
       <c r="C24" s="4" t="inlineStr">
         <is>
-          <t>20,300,000</t>
+          <t>5,949,000</t>
         </is>
       </c>
       <c r="D24" s="4" t="inlineStr">
         <is>
-          <t>7.18%</t>
+          <t>6.97%</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="3" t="inlineStr">
         <is>
-          <t>2454</t>
+          <t>3037</t>
         </is>
       </c>
       <c r="B25" s="3" t="inlineStr">
         <is>
-          <t>聯發科</t>
+          <t>欣興</t>
         </is>
       </c>
       <c r="C25" s="4" t="inlineStr">
         <is>
-          <t>5,088,000</t>
+          <t>20,300,000</t>
         </is>
       </c>
       <c r="D25" s="4" t="inlineStr">
         <is>
-          <t>7.07%</t>
+          <t>6.77%</t>
         </is>
       </c>
     </row>
@@ -726,29 +726,29 @@
       </c>
       <c r="D26" s="4" t="inlineStr">
         <is>
-          <t>5.47%</t>
+          <t>5.83%</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="3" t="inlineStr">
         <is>
-          <t>3653</t>
+          <t>2345</t>
         </is>
       </c>
       <c r="B27" s="3" t="inlineStr">
         <is>
-          <t>健策</t>
+          <t>智邦</t>
         </is>
       </c>
       <c r="C27" s="4" t="inlineStr">
         <is>
-          <t>2,397,000</t>
+          <t>6,464,000</t>
         </is>
       </c>
       <c r="D27" s="4" t="inlineStr">
         <is>
-          <t>5.08%</t>
+          <t>4.89%</t>
         </is>
       </c>
     </row>
@@ -770,51 +770,51 @@
       </c>
       <c r="D28" s="4" t="inlineStr">
         <is>
-          <t>4.82%</t>
+          <t>4.87%</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="3" t="inlineStr">
         <is>
-          <t>2308</t>
+          <t>3653</t>
         </is>
       </c>
       <c r="B29" s="3" t="inlineStr">
         <is>
-          <t>台達電</t>
+          <t>健策</t>
         </is>
       </c>
       <c r="C29" s="4" t="inlineStr">
         <is>
-          <t>7,240,000</t>
+          <t>2,397,000</t>
         </is>
       </c>
       <c r="D29" s="4" t="inlineStr">
         <is>
-          <t>4.72%</t>
+          <t>4.84%</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="3" t="inlineStr">
         <is>
-          <t>2345</t>
+          <t>2308</t>
         </is>
       </c>
       <c r="B30" s="3" t="inlineStr">
         <is>
-          <t>智邦</t>
+          <t>台達電</t>
         </is>
       </c>
       <c r="C30" s="4" t="inlineStr">
         <is>
-          <t>6,464,000</t>
+          <t>7,240,000</t>
         </is>
       </c>
       <c r="D30" s="4" t="inlineStr">
         <is>
-          <t>4.66%</t>
+          <t>4.64%</t>
         </is>
       </c>
     </row>
@@ -836,51 +836,51 @@
       </c>
       <c r="D31" s="4" t="inlineStr">
         <is>
-          <t>4.50%</t>
+          <t>4.60%</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="3" t="inlineStr">
         <is>
-          <t>8046</t>
+          <t>2303</t>
         </is>
       </c>
       <c r="B32" s="3" t="inlineStr">
         <is>
-          <t>南電</t>
+          <t>聯電</t>
         </is>
       </c>
       <c r="C32" s="4" t="inlineStr">
         <is>
-          <t>9,474,000</t>
+          <t>89,118,000</t>
         </is>
       </c>
       <c r="D32" s="4" t="inlineStr">
         <is>
-          <t>4.13%</t>
+          <t>4.06%</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="3" t="inlineStr">
         <is>
-          <t>2303</t>
+          <t>8046</t>
         </is>
       </c>
       <c r="B33" s="3" t="inlineStr">
         <is>
-          <t>聯電</t>
+          <t>南電</t>
         </is>
       </c>
       <c r="C33" s="4" t="inlineStr">
         <is>
-          <t>89,118,000</t>
+          <t>9,474,000</t>
         </is>
       </c>
       <c r="D33" s="4" t="inlineStr">
         <is>
-          <t>4.07%</t>
+          <t>3.99%</t>
         </is>
       </c>
     </row>
@@ -902,7 +902,7 @@
       </c>
       <c r="D34" s="4" t="inlineStr">
         <is>
-          <t>3.86%</t>
+          <t>3.91%</t>
         </is>
       </c>
     </row>
@@ -924,7 +924,7 @@
       </c>
       <c r="D35" s="4" t="inlineStr">
         <is>
-          <t>3.53%</t>
+          <t>3.65%</t>
         </is>
       </c>
     </row>
@@ -946,7 +946,7 @@
       </c>
       <c r="D36" s="4" t="inlineStr">
         <is>
-          <t>2.74%</t>
+          <t>2.69%</t>
         </is>
       </c>
     </row>
@@ -968,7 +968,7 @@
       </c>
       <c r="D37" s="4" t="inlineStr">
         <is>
-          <t>2.21%</t>
+          <t>2.20%</t>
         </is>
       </c>
     </row>
@@ -990,51 +990,51 @@
       </c>
       <c r="D38" s="4" t="inlineStr">
         <is>
-          <t>1.41%</t>
+          <t>1.36%</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="3" t="inlineStr">
         <is>
-          <t>5274</t>
+          <t>2449</t>
         </is>
       </c>
       <c r="B39" s="3" t="inlineStr">
         <is>
-          <t>信驊</t>
+          <t>京元電子</t>
         </is>
       </c>
       <c r="C39" s="4" t="inlineStr">
         <is>
-          <t>207,900</t>
+          <t>12,818,450</t>
         </is>
       </c>
       <c r="D39" s="4" t="inlineStr">
         <is>
-          <t>1.18%</t>
+          <t>1.23%</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="3" t="inlineStr">
         <is>
-          <t>2449</t>
+          <t>5274</t>
         </is>
       </c>
       <c r="B40" s="3" t="inlineStr">
         <is>
-          <t>京元電子</t>
+          <t>信驊</t>
         </is>
       </c>
       <c r="C40" s="4" t="inlineStr">
         <is>
-          <t>12,818,450</t>
+          <t>207,900</t>
         </is>
       </c>
       <c r="D40" s="4" t="inlineStr">
         <is>
-          <t>1.17%</t>
+          <t>1.22%</t>
         </is>
       </c>
     </row>
@@ -1078,51 +1078,51 @@
       </c>
       <c r="D42" s="4" t="inlineStr">
         <is>
-          <t>0.70%</t>
+          <t>0.67%</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="3" t="inlineStr">
         <is>
-          <t>4979</t>
+          <t>2368</t>
         </is>
       </c>
       <c r="B43" s="3" t="inlineStr">
         <is>
-          <t>華星光</t>
+          <t>金像電</t>
         </is>
       </c>
       <c r="C43" s="4" t="inlineStr">
         <is>
-          <t>3,173,000</t>
+          <t>1,457,000</t>
         </is>
       </c>
       <c r="D43" s="4" t="inlineStr">
         <is>
-          <t>0.68%</t>
+          <t>0.61%</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="3" t="inlineStr">
         <is>
-          <t>2368</t>
+          <t>4979</t>
         </is>
       </c>
       <c r="B44" s="3" t="inlineStr">
         <is>
-          <t>金像電</t>
+          <t>華星光</t>
         </is>
       </c>
       <c r="C44" s="4" t="inlineStr">
         <is>
-          <t>1,457,000</t>
+          <t>2,838,000</t>
         </is>
       </c>
       <c r="D44" s="4" t="inlineStr">
         <is>
-          <t>0.60%</t>
+          <t>0.58%</t>
         </is>
       </c>
     </row>
@@ -1144,7 +1144,7 @@
       </c>
       <c r="D45" s="4" t="inlineStr">
         <is>
-          <t>0.54%</t>
+          <t>0.52%</t>
         </is>
       </c>
     </row>
@@ -1166,7 +1166,7 @@
       </c>
       <c r="D46" s="4" t="inlineStr">
         <is>
-          <t>0.48%</t>
+          <t>0.51%</t>
         </is>
       </c>
     </row>
@@ -1205,12 +1205,12 @@
       </c>
       <c r="C48" s="4" t="inlineStr">
         <is>
-          <t>1,644,000</t>
+          <t>2,157,000</t>
         </is>
       </c>
       <c r="D48" s="4" t="inlineStr">
         <is>
-          <t>0.29%</t>
+          <t>0.40%</t>
         </is>
       </c>
     </row>
@@ -1232,7 +1232,7 @@
       </c>
       <c r="D49" s="4" t="inlineStr">
         <is>
-          <t>0.23%</t>
+          <t>0.22%</t>
         </is>
       </c>
     </row>
@@ -1254,7 +1254,7 @@
       </c>
       <c r="D50" s="4" t="inlineStr">
         <is>
-          <t>0.17%</t>
+          <t>0.18%</t>
         </is>
       </c>
     </row>
@@ -1283,100 +1283,100 @@
     <row r="52">
       <c r="A52" s="3" t="inlineStr">
         <is>
-          <t>6191</t>
+          <t>6515</t>
         </is>
       </c>
       <c r="B52" s="3" t="inlineStr">
         <is>
-          <t>精成科</t>
+          <t>穎崴</t>
         </is>
       </c>
       <c r="C52" s="4" t="inlineStr">
         <is>
-          <t>3,988,000</t>
+          <t>54,000</t>
         </is>
       </c>
       <c r="D52" s="4" t="inlineStr">
         <is>
-          <t>0.12%</t>
+          <t>0.13%</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="3" t="inlineStr">
         <is>
-          <t>2313</t>
+          <t>6191</t>
         </is>
       </c>
       <c r="B53" s="3" t="inlineStr">
         <is>
-          <t>華通</t>
+          <t>精成科</t>
         </is>
       </c>
       <c r="C53" s="4" t="inlineStr">
         <is>
-          <t>501,000</t>
+          <t>3,988,000</t>
         </is>
       </c>
       <c r="D53" s="4" t="inlineStr">
         <is>
-          <t>0.04%</t>
+          <t>0.12%</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="3" t="inlineStr">
         <is>
-          <t>2002</t>
+          <t>2313</t>
         </is>
       </c>
       <c r="B54" s="3" t="inlineStr">
         <is>
-          <t>中鋼</t>
+          <t>華通</t>
         </is>
       </c>
       <c r="C54" s="4" t="inlineStr">
         <is>
-          <t>5,163,000</t>
+          <t>501,000</t>
         </is>
       </c>
       <c r="D54" s="4" t="inlineStr">
         <is>
-          <t>0.03%</t>
+          <t>0.04%</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" s="3" t="inlineStr">
         <is>
-          <t>1590</t>
+          <t>2002</t>
         </is>
       </c>
       <c r="B55" s="3" t="inlineStr">
         <is>
-          <t>亞德客-KY</t>
+          <t>中鋼</t>
         </is>
       </c>
       <c r="C55" s="4" t="inlineStr">
         <is>
-          <t>1,000</t>
+          <t>5,163,000</t>
         </is>
       </c>
       <c r="D55" s="4" t="inlineStr">
         <is>
-          <t>0.00%</t>
+          <t>0.03%</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" s="3" t="inlineStr">
         <is>
-          <t>2317</t>
+          <t>8358</t>
         </is>
       </c>
       <c r="B56" s="3" t="inlineStr">
         <is>
-          <t>鴻海</t>
+          <t>金居</t>
         </is>
       </c>
       <c r="C56" s="4" t="inlineStr">
@@ -1393,12 +1393,12 @@
     <row r="57">
       <c r="A57" s="3" t="inlineStr">
         <is>
-          <t>2360</t>
+          <t>6488</t>
         </is>
       </c>
       <c r="B57" s="3" t="inlineStr">
         <is>
-          <t>致茂</t>
+          <t>環球晶</t>
         </is>
       </c>
       <c r="C57" s="4" t="inlineStr">
@@ -1415,12 +1415,12 @@
     <row r="58">
       <c r="A58" s="3" t="inlineStr">
         <is>
-          <t>2382</t>
+          <t>8150</t>
         </is>
       </c>
       <c r="B58" s="3" t="inlineStr">
         <is>
-          <t>廣達</t>
+          <t>南茂</t>
         </is>
       </c>
       <c r="C58" s="4" t="inlineStr">
@@ -1437,12 +1437,12 @@
     <row r="59">
       <c r="A59" s="3" t="inlineStr">
         <is>
-          <t>2408</t>
+          <t>3661</t>
         </is>
       </c>
       <c r="B59" s="3" t="inlineStr">
         <is>
-          <t>南亞科</t>
+          <t>世芯-KY</t>
         </is>
       </c>
       <c r="C59" s="4" t="inlineStr">
@@ -1459,12 +1459,12 @@
     <row r="60">
       <c r="A60" s="3" t="inlineStr">
         <is>
-          <t>2439</t>
+          <t>5347</t>
         </is>
       </c>
       <c r="B60" s="3" t="inlineStr">
         <is>
-          <t>美律</t>
+          <t>世界</t>
         </is>
       </c>
       <c r="C60" s="4" t="inlineStr">
@@ -1481,17 +1481,17 @@
     <row r="61">
       <c r="A61" s="3" t="inlineStr">
         <is>
-          <t>2481</t>
+          <t>6187</t>
         </is>
       </c>
       <c r="B61" s="3" t="inlineStr">
         <is>
-          <t>強茂</t>
+          <t>萬潤</t>
         </is>
       </c>
       <c r="C61" s="4" t="inlineStr">
         <is>
-          <t>5,000</t>
+          <t>8,000</t>
         </is>
       </c>
       <c r="D61" s="4" t="inlineStr">
@@ -1503,12 +1503,12 @@
     <row r="62">
       <c r="A62" s="3" t="inlineStr">
         <is>
-          <t>2637</t>
+          <t>4966</t>
         </is>
       </c>
       <c r="B62" s="3" t="inlineStr">
         <is>
-          <t>慧洋-KY</t>
+          <t>譜瑞-KY</t>
         </is>
       </c>
       <c r="C62" s="4" t="inlineStr">
@@ -1525,12 +1525,12 @@
     <row r="63">
       <c r="A63" s="3" t="inlineStr">
         <is>
-          <t>3008</t>
+          <t>2317</t>
         </is>
       </c>
       <c r="B63" s="3" t="inlineStr">
         <is>
-          <t>大立光</t>
+          <t>鴻海</t>
         </is>
       </c>
       <c r="C63" s="4" t="inlineStr">
@@ -1547,12 +1547,12 @@
     <row r="64">
       <c r="A64" s="3" t="inlineStr">
         <is>
-          <t>5347</t>
+          <t>2360</t>
         </is>
       </c>
       <c r="B64" s="3" t="inlineStr">
         <is>
-          <t>世界</t>
+          <t>致茂</t>
         </is>
       </c>
       <c r="C64" s="4" t="inlineStr">
@@ -1569,17 +1569,17 @@
     <row r="65">
       <c r="A65" s="3" t="inlineStr">
         <is>
-          <t>6187</t>
+          <t>2382</t>
         </is>
       </c>
       <c r="B65" s="3" t="inlineStr">
         <is>
-          <t>萬潤</t>
+          <t>廣達</t>
         </is>
       </c>
       <c r="C65" s="4" t="inlineStr">
         <is>
-          <t>8,000</t>
+          <t>1,000</t>
         </is>
       </c>
       <c r="D65" s="4" t="inlineStr">
@@ -1591,12 +1591,12 @@
     <row r="66">
       <c r="A66" s="3" t="inlineStr">
         <is>
-          <t>4966</t>
+          <t>2408</t>
         </is>
       </c>
       <c r="B66" s="3" t="inlineStr">
         <is>
-          <t>譜瑞-KY</t>
+          <t>南亞科</t>
         </is>
       </c>
       <c r="C66" s="4" t="inlineStr">
@@ -1613,12 +1613,12 @@
     <row r="67">
       <c r="A67" s="3" t="inlineStr">
         <is>
-          <t>3661</t>
+          <t>2439</t>
         </is>
       </c>
       <c r="B67" s="3" t="inlineStr">
         <is>
-          <t>世芯-KY</t>
+          <t>美律</t>
         </is>
       </c>
       <c r="C67" s="4" t="inlineStr">
@@ -1635,17 +1635,17 @@
     <row r="68">
       <c r="A68" s="3" t="inlineStr">
         <is>
-          <t>6488</t>
+          <t>2481</t>
         </is>
       </c>
       <c r="B68" s="3" t="inlineStr">
         <is>
-          <t>環球晶</t>
+          <t>強茂</t>
         </is>
       </c>
       <c r="C68" s="4" t="inlineStr">
         <is>
-          <t>1,000</t>
+          <t>5,000</t>
         </is>
       </c>
       <c r="D68" s="4" t="inlineStr">
@@ -1657,12 +1657,12 @@
     <row r="69">
       <c r="A69" s="3" t="inlineStr">
         <is>
-          <t>6515</t>
+          <t>2637</t>
         </is>
       </c>
       <c r="B69" s="3" t="inlineStr">
         <is>
-          <t>穎崴</t>
+          <t>慧洋-KY</t>
         </is>
       </c>
       <c r="C69" s="4" t="inlineStr">
@@ -1679,12 +1679,12 @@
     <row r="70">
       <c r="A70" s="3" t="inlineStr">
         <is>
-          <t>8358</t>
+          <t>3008</t>
         </is>
       </c>
       <c r="B70" s="3" t="inlineStr">
         <is>
-          <t>金居</t>
+          <t>大立光</t>
         </is>
       </c>
       <c r="C70" s="4" t="inlineStr">
@@ -1701,12 +1701,12 @@
     <row r="71">
       <c r="A71" s="3" t="inlineStr">
         <is>
-          <t>8150</t>
+          <t>1590</t>
         </is>
       </c>
       <c r="B71" s="3" t="inlineStr">
         <is>
-          <t>南茂</t>
+          <t>亞德客-KY</t>
         </is>
       </c>
       <c r="C71" s="4" t="inlineStr">
@@ -1733,7 +1733,7 @@
       </c>
       <c r="C72" s="4" t="inlineStr">
         <is>
-          <t>3,717,284,629</t>
+          <t>6,193,612,047</t>
         </is>
       </c>
       <c r="D72" s="4" t="inlineStr"/>
@@ -1751,7 +1751,7 @@
       </c>
       <c r="C73" s="4" t="inlineStr">
         <is>
-          <t>1,875,546,338</t>
+          <t>2,041,765,538</t>
         </is>
       </c>
       <c r="D73" s="4" t="inlineStr"/>
@@ -1769,7 +1769,7 @@
       </c>
       <c r="C74" s="4" t="inlineStr">
         <is>
-          <t>8,514,045,256</t>
+          <t>6,058,623,693</t>
         </is>
       </c>
       <c r="D74" s="4" t="inlineStr"/>
@@ -1787,7 +1787,7 @@
       </c>
       <c r="C75" s="4" t="inlineStr">
         <is>
-          <t>2,133,377,861</t>
+          <t>813,000,000</t>
         </is>
       </c>
       <c r="D75" s="4" t="inlineStr"/>
